--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437810</v>
+        <v>121438015</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518995</v>
+        <v>518992</v>
       </c>
       <c r="R2" t="n">
-        <v>6994925</v>
+        <v>6994930</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437377</v>
+        <v>121438509</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>79683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,50 +799,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518928</v>
+        <v>519028</v>
       </c>
       <c r="R3" t="n">
-        <v>6995030</v>
+        <v>6994958</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121438509</v>
+        <v>121438476</v>
       </c>
       <c r="B5" t="n">
-        <v>79683</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,40 +1031,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519028</v>
+        <v>519033</v>
       </c>
       <c r="R5" t="n">
-        <v>6994958</v>
+        <v>6994950</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1136,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121438015</v>
+        <v>121437295</v>
       </c>
       <c r="B6" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518992</v>
+        <v>518934</v>
       </c>
       <c r="R6" t="n">
-        <v>6994930</v>
+        <v>6995107</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121438476</v>
+        <v>121437740</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519033</v>
+        <v>518939</v>
       </c>
       <c r="R7" t="n">
-        <v>6994950</v>
+        <v>6994949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437740</v>
+        <v>121437810</v>
       </c>
       <c r="B8" t="n">
         <v>78601</v>
@@ -1400,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518939</v>
+        <v>518995</v>
       </c>
       <c r="R8" t="n">
-        <v>6994949</v>
+        <v>6994925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121437295</v>
+        <v>121437377</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,38 +1475,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518934</v>
+        <v>518928</v>
       </c>
       <c r="R9" t="n">
-        <v>6995107</v>
+        <v>6995030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121438015</v>
+        <v>121437845</v>
       </c>
       <c r="B2" t="n">
-        <v>79683</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518992</v>
+        <v>518997</v>
       </c>
       <c r="R2" t="n">
-        <v>6994930</v>
+        <v>6994931</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121438509</v>
+        <v>121437740</v>
       </c>
       <c r="B3" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519028</v>
+        <v>518939</v>
       </c>
       <c r="R3" t="n">
-        <v>6994958</v>
+        <v>6994949</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437845</v>
+        <v>121437810</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518997</v>
+        <v>518995</v>
       </c>
       <c r="R4" t="n">
-        <v>6994931</v>
+        <v>6994925</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1014,7 @@
         <v>121438476</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121437295</v>
+        <v>121438509</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,37 +1139,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518934</v>
+        <v>519028</v>
       </c>
       <c r="R6" t="n">
-        <v>6995107</v>
+        <v>6994958</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,6 +1220,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121437740</v>
+        <v>121437377</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,38 +1251,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518939</v>
+        <v>518928</v>
       </c>
       <c r="R7" t="n">
-        <v>6994949</v>
+        <v>6995030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437810</v>
+        <v>121438015</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518995</v>
+        <v>518992</v>
       </c>
       <c r="R8" t="n">
-        <v>6994925</v>
+        <v>6994930</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121437377</v>
+        <v>121437295</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,47 +1484,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518928</v>
+        <v>518934</v>
       </c>
       <c r="R9" t="n">
-        <v>6995030</v>
+        <v>6995107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437845</v>
+        <v>121437377</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518997</v>
+        <v>518928</v>
       </c>
       <c r="R2" t="n">
-        <v>6994931</v>
+        <v>6995030</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437740</v>
+        <v>121438476</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518939</v>
+        <v>519033</v>
       </c>
       <c r="R3" t="n">
-        <v>6994949</v>
+        <v>6994950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437810</v>
+        <v>121438509</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>79686</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +924,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518995</v>
+        <v>519028</v>
       </c>
       <c r="R4" t="n">
-        <v>6994925</v>
+        <v>6994958</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +1005,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121438476</v>
+        <v>121437845</v>
       </c>
       <c r="B5" t="n">
         <v>79685</v>
@@ -1051,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519033</v>
+        <v>518997</v>
       </c>
       <c r="R5" t="n">
-        <v>6994950</v>
+        <v>6994931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121438509</v>
+        <v>121437810</v>
       </c>
       <c r="B6" t="n">
-        <v>79686</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,40 +1152,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519028</v>
+        <v>518995</v>
       </c>
       <c r="R6" t="n">
-        <v>6994958</v>
+        <v>6994925</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1230,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121437377</v>
+        <v>121438015</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>79686</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,50 +1260,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518928</v>
+        <v>518992</v>
       </c>
       <c r="R7" t="n">
-        <v>6995030</v>
+        <v>6994930</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121438015</v>
+        <v>121437740</v>
       </c>
       <c r="B8" t="n">
-        <v>79686</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518992</v>
+        <v>518939</v>
       </c>
       <c r="R8" t="n">
-        <v>6994930</v>
+        <v>6994949</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121437377</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121438476</v>
+        <v>121438509</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,37 +812,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519033</v>
+        <v>519028</v>
       </c>
       <c r="R3" t="n">
-        <v>6994950</v>
+        <v>6994958</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121438509</v>
+        <v>121437810</v>
       </c>
       <c r="B4" t="n">
-        <v>79686</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,40 +928,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519028</v>
+        <v>518995</v>
       </c>
       <c r="R4" t="n">
-        <v>6994958</v>
+        <v>6994925</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1006,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121437845</v>
+        <v>121437740</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518997</v>
+        <v>518939</v>
       </c>
       <c r="R5" t="n">
-        <v>6994931</v>
+        <v>6994949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121437810</v>
+        <v>121438015</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>79689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518995</v>
+        <v>518992</v>
       </c>
       <c r="R6" t="n">
-        <v>6994925</v>
+        <v>6994930</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121438015</v>
+        <v>121437295</v>
       </c>
       <c r="B7" t="n">
-        <v>79686</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518992</v>
+        <v>518934</v>
       </c>
       <c r="R7" t="n">
-        <v>6994930</v>
+        <v>6995107</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437740</v>
+        <v>121437845</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518939</v>
+        <v>518997</v>
       </c>
       <c r="R8" t="n">
-        <v>6994949</v>
+        <v>6994931</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121437295</v>
+        <v>121438476</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518934</v>
+        <v>519033</v>
       </c>
       <c r="R9" t="n">
-        <v>6995107</v>
+        <v>6994950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437810</v>
+        <v>121438015</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518995</v>
+        <v>518992</v>
       </c>
       <c r="R4" t="n">
-        <v>6994925</v>
+        <v>6994930</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121437740</v>
+        <v>121438476</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518939</v>
+        <v>519033</v>
       </c>
       <c r="R5" t="n">
-        <v>6994949</v>
+        <v>6994950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121438015</v>
+        <v>121437845</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518992</v>
+        <v>518997</v>
       </c>
       <c r="R6" t="n">
-        <v>6994930</v>
+        <v>6994931</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121437295</v>
+        <v>121437740</v>
       </c>
       <c r="B7" t="n">
         <v>78607</v>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518934</v>
+        <v>518939</v>
       </c>
       <c r="R7" t="n">
-        <v>6995107</v>
+        <v>6994949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437845</v>
+        <v>121437295</v>
       </c>
       <c r="B8" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518997</v>
+        <v>518934</v>
       </c>
       <c r="R8" t="n">
-        <v>6994931</v>
+        <v>6995107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121438476</v>
+        <v>121437810</v>
       </c>
       <c r="B9" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519033</v>
+        <v>518995</v>
       </c>
       <c r="R9" t="n">
-        <v>6994950</v>
+        <v>6994925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1582,6 +1582,1032 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121541170</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>519001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6994976</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121539367</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518958</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6994938</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121541065</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98099</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>518958</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6995111</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121539600</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98099</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>518930</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6994966</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121541218</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>518920</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6994929</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121540788</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90714</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>518929</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6995040</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121541196</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>518957</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6994989</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121541194</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>518957</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6994989</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121541163</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>518997</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6994966</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437377</v>
+        <v>121438015</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518928</v>
+        <v>518992</v>
       </c>
       <c r="R2" t="n">
-        <v>6995030</v>
+        <v>6994930</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121438509</v>
+        <v>121437740</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,40 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519028</v>
+        <v>518939</v>
       </c>
       <c r="R3" t="n">
-        <v>6994958</v>
+        <v>6994949</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121438015</v>
+        <v>121437810</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518992</v>
+        <v>518995</v>
       </c>
       <c r="R4" t="n">
-        <v>6994930</v>
+        <v>6994925</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121438476</v>
+        <v>121437377</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519033</v>
+        <v>518928</v>
       </c>
       <c r="R5" t="n">
-        <v>6994950</v>
+        <v>6995030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1135,7 @@
         <v>121437845</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121437740</v>
+        <v>121438476</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518939</v>
+        <v>519033</v>
       </c>
       <c r="R7" t="n">
-        <v>6994949</v>
+        <v>6994950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437295</v>
+        <v>121438509</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,37 +1372,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518934</v>
+        <v>519028</v>
       </c>
       <c r="R8" t="n">
-        <v>6995107</v>
+        <v>6994958</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,6 +1453,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121437810</v>
+        <v>121437295</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518995</v>
+        <v>518934</v>
       </c>
       <c r="R9" t="n">
-        <v>6994925</v>
+        <v>6995107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541170</v>
+        <v>121540788</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519001</v>
+        <v>518929</v>
       </c>
       <c r="R10" t="n">
-        <v>6994976</v>
+        <v>6995040</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121539367</v>
+        <v>121541196</v>
       </c>
       <c r="B11" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518958</v>
+        <v>518957</v>
       </c>
       <c r="R11" t="n">
-        <v>6994938</v>
+        <v>6994989</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541065</v>
+        <v>121539600</v>
       </c>
       <c r="B12" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518958</v>
+        <v>518930</v>
       </c>
       <c r="R12" t="n">
-        <v>6995111</v>
+        <v>6994966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121539600</v>
+        <v>121541065</v>
       </c>
       <c r="B13" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518930</v>
+        <v>518958</v>
       </c>
       <c r="R13" t="n">
-        <v>6994966</v>
+        <v>6995111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,7 +2050,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541218</v>
+        <v>121541163</v>
       </c>
       <c r="B14" t="n">
         <v>79689</v>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518920</v>
+        <v>518997</v>
       </c>
       <c r="R14" t="n">
-        <v>6994929</v>
+        <v>6994966</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121540788</v>
+        <v>121541170</v>
       </c>
       <c r="B15" t="n">
-        <v>90714</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,21 +2178,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518929</v>
+        <v>519001</v>
       </c>
       <c r="R15" t="n">
-        <v>6995040</v>
+        <v>6994976</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121541196</v>
+        <v>121539367</v>
       </c>
       <c r="B16" t="n">
-        <v>79690</v>
+        <v>79689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,21 +2290,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518957</v>
+        <v>518958</v>
       </c>
       <c r="R16" t="n">
-        <v>6994989</v>
+        <v>6994938</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541163</v>
+        <v>121541218</v>
       </c>
       <c r="B18" t="n">
         <v>79689</v>
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518997</v>
+        <v>518920</v>
       </c>
       <c r="R18" t="n">
-        <v>6994966</v>
+        <v>6994929</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121438015</v>
+        <v>121437295</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518992</v>
+        <v>518934</v>
       </c>
       <c r="R2" t="n">
-        <v>6994930</v>
+        <v>6995107</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437740</v>
+        <v>121437377</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518939</v>
+        <v>518928</v>
       </c>
       <c r="R3" t="n">
-        <v>6994949</v>
+        <v>6995030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437810</v>
+        <v>121437845</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518995</v>
+        <v>518997</v>
       </c>
       <c r="R4" t="n">
-        <v>6994925</v>
+        <v>6994931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121437377</v>
+        <v>121437740</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,47 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518928</v>
+        <v>518939</v>
       </c>
       <c r="R5" t="n">
-        <v>6995030</v>
+        <v>6994949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121437845</v>
+        <v>121437810</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518997</v>
+        <v>518995</v>
       </c>
       <c r="R6" t="n">
-        <v>6994931</v>
+        <v>6994925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
         <v>121438476</v>
       </c>
       <c r="B7" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>121438509</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121437295</v>
+        <v>121438015</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518934</v>
+        <v>518992</v>
       </c>
       <c r="R9" t="n">
-        <v>6995107</v>
+        <v>6994930</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121540788</v>
+        <v>121541194</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518929</v>
+        <v>518957</v>
       </c>
       <c r="R10" t="n">
-        <v>6995040</v>
+        <v>6994989</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541196</v>
+        <v>121541218</v>
       </c>
       <c r="B11" t="n">
         <v>79690</v>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518957</v>
+        <v>518920</v>
       </c>
       <c r="R11" t="n">
-        <v>6994989</v>
+        <v>6994929</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121539600</v>
+        <v>121541196</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>79691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,50 +1820,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518930</v>
+        <v>518957</v>
       </c>
       <c r="R12" t="n">
-        <v>6994966</v>
+        <v>6994989</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,7 +1923,7 @@
         <v>121541065</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2050,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541163</v>
+        <v>121539367</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,13 +2081,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518997</v>
+        <v>518958</v>
       </c>
       <c r="R14" t="n">
-        <v>6994966</v>
+        <v>6994938</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2125,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,7 +2153,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121541170</v>
+        <v>121541163</v>
       </c>
       <c r="B15" t="n">
         <v>79690</v>
@@ -2178,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519001</v>
+        <v>518997</v>
       </c>
       <c r="R15" t="n">
-        <v>6994976</v>
+        <v>6994966</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2237,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121539367</v>
+        <v>121541170</v>
       </c>
       <c r="B16" t="n">
-        <v>79689</v>
+        <v>79691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,21 +2281,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,13 +2305,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518958</v>
+        <v>519001</v>
       </c>
       <c r="R16" t="n">
-        <v>6994938</v>
+        <v>6994976</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541194</v>
+        <v>121539600</v>
       </c>
       <c r="B17" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,38 +2389,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518957</v>
+        <v>518930</v>
       </c>
       <c r="R17" t="n">
-        <v>6994989</v>
+        <v>6994966</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541218</v>
+        <v>121540788</v>
       </c>
       <c r="B18" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518920</v>
+        <v>518929</v>
       </c>
       <c r="R18" t="n">
-        <v>6994929</v>
+        <v>6995040</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437295</v>
+        <v>121437810</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518934</v>
+        <v>518995</v>
       </c>
       <c r="R2" t="n">
-        <v>6995107</v>
+        <v>6994925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437377</v>
+        <v>121437295</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518928</v>
+        <v>518934</v>
       </c>
       <c r="R3" t="n">
-        <v>6995030</v>
+        <v>6995107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437845</v>
+        <v>121437377</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518997</v>
+        <v>518928</v>
       </c>
       <c r="R4" t="n">
-        <v>6994931</v>
+        <v>6995030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121437740</v>
+        <v>121437845</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518939</v>
+        <v>518997</v>
       </c>
       <c r="R5" t="n">
-        <v>6994949</v>
+        <v>6994931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121437810</v>
+        <v>121438015</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518995</v>
+        <v>518992</v>
       </c>
       <c r="R6" t="n">
-        <v>6994925</v>
+        <v>6994930</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121438509</v>
+        <v>121437740</v>
       </c>
       <c r="B8" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,40 +1372,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519028</v>
+        <v>518939</v>
       </c>
       <c r="R8" t="n">
-        <v>6994958</v>
+        <v>6994949</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,7 +1450,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,7 +1468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121438015</v>
+        <v>121438509</v>
       </c>
       <c r="B9" t="n">
         <v>79691</v>
@@ -1506,16 +1502,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518992</v>
+        <v>519028</v>
       </c>
       <c r="R9" t="n">
-        <v>6994930</v>
+        <v>6994958</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1547,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,6 +1565,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541194</v>
+        <v>121539367</v>
       </c>
       <c r="B10" t="n">
         <v>79690</v>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518957</v>
+        <v>518958</v>
       </c>
       <c r="R10" t="n">
-        <v>6994989</v>
+        <v>6994938</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541218</v>
+        <v>121541170</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518920</v>
+        <v>519001</v>
       </c>
       <c r="R11" t="n">
-        <v>6994929</v>
+        <v>6994976</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541065</v>
+        <v>121539600</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518958</v>
+        <v>518930</v>
       </c>
       <c r="R13" t="n">
-        <v>6995111</v>
+        <v>6994966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121539367</v>
+        <v>121541218</v>
       </c>
       <c r="B14" t="n">
         <v>79690</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518958</v>
+        <v>518920</v>
       </c>
       <c r="R14" t="n">
-        <v>6994938</v>
+        <v>6994929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121541163</v>
+        <v>121540788</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,13 +2193,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518997</v>
+        <v>518929</v>
       </c>
       <c r="R15" t="n">
-        <v>6994966</v>
+        <v>6995040</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121541170</v>
+        <v>121541163</v>
       </c>
       <c r="B16" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519001</v>
+        <v>518997</v>
       </c>
       <c r="R16" t="n">
-        <v>6994976</v>
+        <v>6994966</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121539600</v>
+        <v>121541065</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518930</v>
+        <v>518958</v>
       </c>
       <c r="R17" t="n">
-        <v>6994966</v>
+        <v>6995111</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121540788</v>
+        <v>121541194</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518929</v>
+        <v>518957</v>
       </c>
       <c r="R18" t="n">
-        <v>6995040</v>
+        <v>6994989</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437810</v>
+        <v>121437740</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518995</v>
+        <v>518939</v>
       </c>
       <c r="R2" t="n">
-        <v>6994925</v>
+        <v>6994949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437377</v>
+        <v>121438476</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518928</v>
+        <v>519033</v>
       </c>
       <c r="R4" t="n">
-        <v>6995030</v>
+        <v>6994950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121437845</v>
+        <v>121438509</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,37 +1027,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518997</v>
+        <v>519028</v>
       </c>
       <c r="R5" t="n">
-        <v>6994931</v>
+        <v>6994958</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,6 +1108,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121438015</v>
+        <v>121437845</v>
       </c>
       <c r="B6" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518992</v>
+        <v>518997</v>
       </c>
       <c r="R6" t="n">
-        <v>6994930</v>
+        <v>6994931</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121438476</v>
+        <v>121437810</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519033</v>
+        <v>518995</v>
       </c>
       <c r="R7" t="n">
-        <v>6994950</v>
+        <v>6994925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437740</v>
+        <v>121437377</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,38 +1363,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518939</v>
+        <v>518928</v>
       </c>
       <c r="R8" t="n">
-        <v>6994949</v>
+        <v>6995030</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,7 +1472,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121438509</v>
+        <v>121438015</v>
       </c>
       <c r="B9" t="n">
         <v>79691</v>
@@ -1502,19 +1506,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519028</v>
+        <v>518992</v>
       </c>
       <c r="R9" t="n">
-        <v>6994958</v>
+        <v>6994930</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1546,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,7 +1566,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121539367</v>
+        <v>121541163</v>
       </c>
       <c r="B10" t="n">
         <v>79690</v>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518958</v>
+        <v>518997</v>
       </c>
       <c r="R10" t="n">
-        <v>6994938</v>
+        <v>6994966</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541170</v>
+        <v>121539600</v>
       </c>
       <c r="B11" t="n">
-        <v>79691</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,41 +1708,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519001</v>
+        <v>518930</v>
       </c>
       <c r="R11" t="n">
-        <v>6994976</v>
+        <v>6994966</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121539600</v>
+        <v>121539367</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,47 +1941,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518930</v>
+        <v>518958</v>
       </c>
       <c r="R13" t="n">
-        <v>6994966</v>
+        <v>6994938</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121540788</v>
+        <v>121541170</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>79691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,13 +2193,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518929</v>
+        <v>519001</v>
       </c>
       <c r="R15" t="n">
-        <v>6995040</v>
+        <v>6994976</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121541163</v>
+        <v>121541065</v>
       </c>
       <c r="B16" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,41 +2277,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518997</v>
+        <v>518958</v>
       </c>
       <c r="R16" t="n">
-        <v>6994966</v>
+        <v>6995111</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2340,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541065</v>
+        <v>121541194</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,47 +2398,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518958</v>
+        <v>518957</v>
       </c>
       <c r="R17" t="n">
-        <v>6995111</v>
+        <v>6994989</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541194</v>
+        <v>121540788</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518957</v>
+        <v>518929</v>
       </c>
       <c r="R18" t="n">
-        <v>6994989</v>
+        <v>6995040</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437740</v>
+        <v>121438476</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518939</v>
+        <v>519033</v>
       </c>
       <c r="R2" t="n">
-        <v>6994949</v>
+        <v>6994950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437295</v>
+        <v>121437845</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518934</v>
+        <v>518997</v>
       </c>
       <c r="R3" t="n">
-        <v>6995107</v>
+        <v>6994931</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121438476</v>
+        <v>121437740</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519033</v>
+        <v>518939</v>
       </c>
       <c r="R4" t="n">
-        <v>6994950</v>
+        <v>6994949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121437845</v>
+        <v>121438015</v>
       </c>
       <c r="B6" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518997</v>
+        <v>518992</v>
       </c>
       <c r="R6" t="n">
-        <v>6994931</v>
+        <v>6994930</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121437810</v>
+        <v>121437295</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518995</v>
+        <v>518934</v>
       </c>
       <c r="R7" t="n">
-        <v>6994925</v>
+        <v>6995107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437377</v>
+        <v>121437810</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,47 +1363,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518928</v>
+        <v>518995</v>
       </c>
       <c r="R8" t="n">
-        <v>6995030</v>
+        <v>6994925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121438015</v>
+        <v>121437377</v>
       </c>
       <c r="B9" t="n">
-        <v>79691</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,41 +1475,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518992</v>
+        <v>518928</v>
       </c>
       <c r="R9" t="n">
-        <v>6994930</v>
+        <v>6995030</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541163</v>
+        <v>121541065</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,41 +1596,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518997</v>
+        <v>518958</v>
       </c>
       <c r="R10" t="n">
-        <v>6994966</v>
+        <v>6995111</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121539600</v>
+        <v>121541194</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,47 +1717,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518930</v>
+        <v>518957</v>
       </c>
       <c r="R11" t="n">
-        <v>6994966</v>
+        <v>6994989</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541196</v>
+        <v>121539367</v>
       </c>
       <c r="B12" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518957</v>
+        <v>518958</v>
       </c>
       <c r="R12" t="n">
-        <v>6994989</v>
+        <v>6994938</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121539367</v>
+        <v>121541218</v>
       </c>
       <c r="B13" t="n">
         <v>79690</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518958</v>
+        <v>518920</v>
       </c>
       <c r="R13" t="n">
-        <v>6994938</v>
+        <v>6994929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541218</v>
+        <v>121541170</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518920</v>
+        <v>519001</v>
       </c>
       <c r="R14" t="n">
-        <v>6994929</v>
+        <v>6994976</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121541170</v>
+        <v>121540788</v>
       </c>
       <c r="B15" t="n">
-        <v>79691</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,13 +2193,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519001</v>
+        <v>518929</v>
       </c>
       <c r="R15" t="n">
-        <v>6994976</v>
+        <v>6995040</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,7 +2265,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121541065</v>
+        <v>121539600</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518958</v>
+        <v>518930</v>
       </c>
       <c r="R16" t="n">
-        <v>6995111</v>
+        <v>6994966</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541194</v>
+        <v>121541196</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,21 +2402,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
         <v>6994989</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121540788</v>
+        <v>121541163</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518929</v>
+        <v>518997</v>
       </c>
       <c r="R18" t="n">
-        <v>6995040</v>
+        <v>6994966</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121438476</v>
+        <v>121438015</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519033</v>
+        <v>518992</v>
       </c>
       <c r="R2" t="n">
-        <v>6994950</v>
+        <v>6994930</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437845</v>
+        <v>121437295</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518997</v>
+        <v>518934</v>
       </c>
       <c r="R3" t="n">
-        <v>6994931</v>
+        <v>6995107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437740</v>
+        <v>121437810</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518939</v>
+        <v>518995</v>
       </c>
       <c r="R4" t="n">
-        <v>6994949</v>
+        <v>6994925</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>121438509</v>
       </c>
       <c r="B5" t="n">
-        <v>79691</v>
+        <v>79698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121438015</v>
+        <v>121437845</v>
       </c>
       <c r="B6" t="n">
-        <v>79691</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518992</v>
+        <v>518997</v>
       </c>
       <c r="R6" t="n">
-        <v>6994930</v>
+        <v>6994931</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121437295</v>
+        <v>121437377</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,38 +1251,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518934</v>
+        <v>518928</v>
       </c>
       <c r="R7" t="n">
-        <v>6995107</v>
+        <v>6995030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437810</v>
+        <v>121438476</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518995</v>
+        <v>519033</v>
       </c>
       <c r="R8" t="n">
-        <v>6994925</v>
+        <v>6994950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121437377</v>
+        <v>121437740</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,47 +1484,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518928</v>
+        <v>518939</v>
       </c>
       <c r="R9" t="n">
-        <v>6995030</v>
+        <v>6994949</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541065</v>
+        <v>121541194</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,47 +1596,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518958</v>
+        <v>518957</v>
       </c>
       <c r="R10" t="n">
-        <v>6995111</v>
+        <v>6994989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541194</v>
+        <v>121539367</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518957</v>
+        <v>518958</v>
       </c>
       <c r="R11" t="n">
-        <v>6994989</v>
+        <v>6994938</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121539367</v>
+        <v>121541163</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518958</v>
+        <v>518997</v>
       </c>
       <c r="R12" t="n">
-        <v>6994938</v>
+        <v>6994966</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541218</v>
+        <v>121540788</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,13 +1960,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518920</v>
+        <v>518929</v>
       </c>
       <c r="R13" t="n">
-        <v>6994929</v>
+        <v>6995040</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,7 +2035,7 @@
         <v>121541170</v>
       </c>
       <c r="B14" t="n">
-        <v>79691</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2153,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121540788</v>
+        <v>121539600</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>98113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,41 +2156,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518929</v>
+        <v>518930</v>
       </c>
       <c r="R15" t="n">
-        <v>6995040</v>
+        <v>6994966</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121539600</v>
+        <v>121541218</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>79697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,47 +2277,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518930</v>
+        <v>518920</v>
       </c>
       <c r="R16" t="n">
-        <v>6994966</v>
+        <v>6994929</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,7 +2380,7 @@
         <v>121541196</v>
       </c>
       <c r="B17" t="n">
-        <v>79691</v>
+        <v>79698</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2498,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541163</v>
+        <v>121541065</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,41 +2501,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518997</v>
+        <v>518958</v>
       </c>
       <c r="R18" t="n">
-        <v>6994966</v>
+        <v>6995111</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121438015</v>
+        <v>121437295</v>
       </c>
       <c r="B3" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518992</v>
+        <v>518934</v>
       </c>
       <c r="R3" t="n">
-        <v>6994930</v>
+        <v>6995107</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121437810</v>
+        <v>121438476</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518995</v>
+        <v>519033</v>
       </c>
       <c r="R4" t="n">
-        <v>6994925</v>
+        <v>6994950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121437295</v>
+        <v>121437740</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518934</v>
+        <v>518939</v>
       </c>
       <c r="R5" t="n">
-        <v>6995107</v>
+        <v>6994949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121438476</v>
+        <v>121437810</v>
       </c>
       <c r="B6" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519033</v>
+        <v>518995</v>
       </c>
       <c r="R6" t="n">
-        <v>6994950</v>
+        <v>6994925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121438509</v>
+        <v>121437377</v>
       </c>
       <c r="B7" t="n">
-        <v>79698</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,44 +1247,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519028</v>
+        <v>518928</v>
       </c>
       <c r="R7" t="n">
-        <v>6994958</v>
+        <v>6995030</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1338,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121437377</v>
+        <v>121438509</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>79698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,50 +1368,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518928</v>
+        <v>519028</v>
       </c>
       <c r="R8" t="n">
-        <v>6995030</v>
+        <v>6994958</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,6 +1453,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121437740</v>
+        <v>121438015</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518939</v>
+        <v>518992</v>
       </c>
       <c r="R9" t="n">
-        <v>6994949</v>
+        <v>6994930</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541196</v>
+        <v>121541218</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518957</v>
+        <v>518920</v>
       </c>
       <c r="R10" t="n">
-        <v>6994989</v>
+        <v>6994929</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541218</v>
+        <v>121540788</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518920</v>
+        <v>518929</v>
       </c>
       <c r="R12" t="n">
-        <v>6994929</v>
+        <v>6995040</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541163</v>
+        <v>121541196</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518997</v>
+        <v>518957</v>
       </c>
       <c r="R13" t="n">
-        <v>6994966</v>
+        <v>6994989</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121539367</v>
+        <v>121539600</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,38 +2044,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518958</v>
+        <v>518930</v>
       </c>
       <c r="R14" t="n">
-        <v>6994938</v>
+        <v>6994966</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121539600</v>
+        <v>121539367</v>
       </c>
       <c r="B15" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,47 +2165,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518930</v>
+        <v>518958</v>
       </c>
       <c r="R15" t="n">
-        <v>6994966</v>
+        <v>6994938</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121540788</v>
+        <v>121541065</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,41 +2277,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518929</v>
+        <v>518958</v>
       </c>
       <c r="R16" t="n">
-        <v>6995040</v>
+        <v>6995111</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2340,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541065</v>
+        <v>121541163</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,50 +2510,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518958</v>
+        <v>518997</v>
       </c>
       <c r="R18" t="n">
-        <v>6995111</v>
+        <v>6994966</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541218</v>
+        <v>121540788</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518920</v>
+        <v>518929</v>
       </c>
       <c r="R10" t="n">
-        <v>6994929</v>
+        <v>6995040</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541170</v>
+        <v>121541218</v>
       </c>
       <c r="B11" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519001</v>
+        <v>518920</v>
       </c>
       <c r="R11" t="n">
-        <v>6994976</v>
+        <v>6994929</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121540788</v>
+        <v>121541065</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,41 +1820,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518929</v>
+        <v>518958</v>
       </c>
       <c r="R12" t="n">
-        <v>6995040</v>
+        <v>6995111</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541196</v>
+        <v>121539600</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,41 +1941,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518957</v>
+        <v>518930</v>
       </c>
       <c r="R13" t="n">
-        <v>6994989</v>
+        <v>6994966</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121539600</v>
+        <v>121541196</v>
       </c>
       <c r="B14" t="n">
-        <v>98113</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,50 +2062,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518930</v>
+        <v>518957</v>
       </c>
       <c r="R14" t="n">
-        <v>6994966</v>
+        <v>6994989</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,7 +2162,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121539367</v>
+        <v>121541194</v>
       </c>
       <c r="B15" t="n">
         <v>79697</v>
@@ -2193,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518958</v>
+        <v>518957</v>
       </c>
       <c r="R15" t="n">
-        <v>6994938</v>
+        <v>6994989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121541065</v>
+        <v>121541163</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,50 +2286,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518958</v>
+        <v>518997</v>
       </c>
       <c r="R16" t="n">
-        <v>6995111</v>
+        <v>6994966</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541194</v>
+        <v>121541170</v>
       </c>
       <c r="B17" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,21 +2402,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518957</v>
+        <v>519001</v>
       </c>
       <c r="R17" t="n">
-        <v>6994989</v>
+        <v>6994976</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541163</v>
+        <v>121539367</v>
       </c>
       <c r="B18" t="n">
         <v>79697</v>
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518997</v>
+        <v>518958</v>
       </c>
       <c r="R18" t="n">
-        <v>6994966</v>
+        <v>6994938</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121540788</v>
+        <v>121539367</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518929</v>
+        <v>518958</v>
       </c>
       <c r="R10" t="n">
-        <v>6995040</v>
+        <v>6994938</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541218</v>
+        <v>121540788</v>
       </c>
       <c r="B11" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518920</v>
+        <v>518929</v>
       </c>
       <c r="R11" t="n">
-        <v>6994929</v>
+        <v>6995040</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541065</v>
+        <v>121541194</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,47 +1820,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518958</v>
+        <v>518957</v>
       </c>
       <c r="R12" t="n">
-        <v>6995111</v>
+        <v>6994989</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121539600</v>
+        <v>121541196</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>79698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,50 +1932,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518930</v>
+        <v>518957</v>
       </c>
       <c r="R13" t="n">
-        <v>6994966</v>
+        <v>6994989</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541196</v>
+        <v>121541170</v>
       </c>
       <c r="B14" t="n">
         <v>79698</v>
@@ -2090,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518957</v>
+        <v>519001</v>
       </c>
       <c r="R14" t="n">
-        <v>6994989</v>
+        <v>6994976</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2125,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,7 +2144,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121541194</v>
+        <v>121541163</v>
       </c>
       <c r="B15" t="n">
         <v>79697</v>
@@ -2202,13 +2184,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518957</v>
+        <v>518997</v>
       </c>
       <c r="R15" t="n">
-        <v>6994989</v>
+        <v>6994966</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2237,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121541163</v>
+        <v>121541065</v>
       </c>
       <c r="B16" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,41 +2268,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518997</v>
+        <v>518958</v>
       </c>
       <c r="R16" t="n">
-        <v>6994966</v>
+        <v>6995111</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541170</v>
+        <v>121541218</v>
       </c>
       <c r="B17" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,21 +2393,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2426,13 +2417,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519001</v>
+        <v>518920</v>
       </c>
       <c r="R17" t="n">
-        <v>6994976</v>
+        <v>6994929</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2461,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121539367</v>
+        <v>121539600</v>
       </c>
       <c r="B18" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,38 +2501,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518958</v>
+        <v>518930</v>
       </c>
       <c r="R18" t="n">
-        <v>6994938</v>
+        <v>6994966</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121540788</v>
+        <v>121539600</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,41 +1708,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518929</v>
+        <v>518930</v>
       </c>
       <c r="R11" t="n">
-        <v>6995040</v>
+        <v>6994966</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541194</v>
+        <v>121541196</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,21 +1833,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,7 +1863,7 @@
         <v>6994989</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541196</v>
+        <v>121541065</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,41 +1941,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518957</v>
+        <v>518958</v>
       </c>
       <c r="R13" t="n">
-        <v>6994989</v>
+        <v>6995111</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541170</v>
+        <v>121541218</v>
       </c>
       <c r="B14" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2066,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,13 +2090,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519001</v>
+        <v>518920</v>
       </c>
       <c r="R14" t="n">
-        <v>6994976</v>
+        <v>6994929</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121541163</v>
+        <v>121541170</v>
       </c>
       <c r="B15" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,21 +2178,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2184,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518997</v>
+        <v>519001</v>
       </c>
       <c r="R15" t="n">
-        <v>6994966</v>
+        <v>6994976</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2219,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121541065</v>
+        <v>121540788</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,50 +2286,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518958</v>
+        <v>518929</v>
       </c>
       <c r="R16" t="n">
-        <v>6995111</v>
+        <v>6995040</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2340,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,7 +2386,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541218</v>
+        <v>121541163</v>
       </c>
       <c r="B17" t="n">
         <v>79697</v>
@@ -2417,13 +2426,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518920</v>
+        <v>518997</v>
       </c>
       <c r="R17" t="n">
-        <v>6994929</v>
+        <v>6994966</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2452,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121539600</v>
+        <v>121541194</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,47 +2510,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518930</v>
+        <v>518957</v>
       </c>
       <c r="R18" t="n">
-        <v>6994966</v>
+        <v>6994989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121539367</v>
+        <v>121541170</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518958</v>
+        <v>519001</v>
       </c>
       <c r="R10" t="n">
-        <v>6994938</v>
+        <v>6994976</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541196</v>
+        <v>121541065</v>
       </c>
       <c r="B12" t="n">
-        <v>79698</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,41 +1829,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518957</v>
+        <v>518958</v>
       </c>
       <c r="R12" t="n">
-        <v>6994989</v>
+        <v>6995111</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541065</v>
+        <v>121541196</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>79698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,50 +1950,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518958</v>
+        <v>518957</v>
       </c>
       <c r="R13" t="n">
-        <v>6995111</v>
+        <v>6994989</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,7 +2050,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541218</v>
+        <v>121541194</v>
       </c>
       <c r="B14" t="n">
         <v>79697</v>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518920</v>
+        <v>518957</v>
       </c>
       <c r="R14" t="n">
-        <v>6994929</v>
+        <v>6994989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121541170</v>
+        <v>121541163</v>
       </c>
       <c r="B15" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,21 +2178,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519001</v>
+        <v>518997</v>
       </c>
       <c r="R15" t="n">
-        <v>6994976</v>
+        <v>6994966</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2386,7 +2386,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541163</v>
+        <v>121541218</v>
       </c>
       <c r="B17" t="n">
         <v>79697</v>
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518997</v>
+        <v>518920</v>
       </c>
       <c r="R17" t="n">
-        <v>6994966</v>
+        <v>6994929</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541194</v>
+        <v>121539367</v>
       </c>
       <c r="B18" t="n">
         <v>79697</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518957</v>
+        <v>518958</v>
       </c>
       <c r="R18" t="n">
-        <v>6994989</v>
+        <v>6994938</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 6748-2024 artfynd.xlsx
+++ b/artfynd/A 6748-2024 artfynd.xlsx
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541170</v>
+        <v>121541065</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,41 +1596,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519001</v>
+        <v>518958</v>
       </c>
       <c r="R10" t="n">
-        <v>6994976</v>
+        <v>6995111</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121539600</v>
+        <v>121541196</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>79698</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,50 +1717,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518930</v>
+        <v>518957</v>
       </c>
       <c r="R11" t="n">
-        <v>6994966</v>
+        <v>6994989</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541065</v>
+        <v>121541163</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,50 +1829,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518958</v>
+        <v>518997</v>
       </c>
       <c r="R12" t="n">
-        <v>6995111</v>
+        <v>6994966</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1901,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541196</v>
+        <v>121541170</v>
       </c>
       <c r="B13" t="n">
         <v>79698</v>
@@ -1978,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518957</v>
+        <v>519001</v>
       </c>
       <c r="R13" t="n">
-        <v>6994989</v>
+        <v>6994976</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2013,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121541163</v>
+        <v>121539600</v>
       </c>
       <c r="B15" t="n">
-        <v>79697</v>
+        <v>98113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,41 +2165,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518997</v>
+        <v>518930</v>
       </c>
       <c r="R15" t="n">
         <v>6994966</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121540788</v>
+        <v>121541218</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,21 +2290,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518929</v>
+        <v>518920</v>
       </c>
       <c r="R16" t="n">
-        <v>6995040</v>
+        <v>6994929</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,7 +2386,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121541218</v>
+        <v>121539367</v>
       </c>
       <c r="B17" t="n">
         <v>79697</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518920</v>
+        <v>518958</v>
       </c>
       <c r="R17" t="n">
-        <v>6994929</v>
+        <v>6994938</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121539367</v>
+        <v>121540788</v>
       </c>
       <c r="B18" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518958</v>
+        <v>518929</v>
       </c>
       <c r="R18" t="n">
-        <v>6994938</v>
+        <v>6995040</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
